--- a/ROSA_vitaSPEC/Results/test_pretraitements/SEC/ratio.alpha.beta/Resultats_ratio.alpha.beta_moy_RMSEP.xlsx
+++ b/ROSA_vitaSPEC/Results/test_pretraitements/SEC/ratio.alpha.beta/Resultats_ratio.alpha.beta_moy_RMSEP.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\U108-N806\Documents\STAGE_M2_ROSA_NIRS\VitaSPEC\vitaspec_R\ROSA_vitaSPEC\Results\test_pretraitements\ratio.alpha.beta\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\U108-N806\Documents\STAGE_M2_ROSA_NIRS\VitaSPEC\vitaspec_R\ROSA_vitaSPEC\Results\test_pretraitements\SEC\ratio.alpha.beta\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -620,55 +620,55 @@
         <v>18</v>
       </c>
       <c r="B2">
-        <v>0.41842844126741657</v>
+        <v>0.41842843519780271</v>
       </c>
       <c r="C2">
-        <v>0.48594555921399668</v>
+        <v>0.48594555869191192</v>
       </c>
       <c r="D2">
-        <v>0.48972842429048552</v>
+        <v>0.4897284227825181</v>
       </c>
       <c r="E2">
-        <v>0.49421525964178731</v>
+        <v>0.49421526559359519</v>
       </c>
       <c r="F2">
-        <v>0.4956173537110643</v>
+        <v>0.49561735452763339</v>
       </c>
       <c r="G2">
-        <v>0.49594335816417551</v>
+        <v>0.4959433555707316</v>
       </c>
       <c r="H2">
-        <v>0.49578859301752409</v>
+        <v>0.49578858986449847</v>
       </c>
       <c r="I2">
-        <v>0.49612088007914962</v>
+        <v>0.49612087737154159</v>
       </c>
       <c r="J2">
-        <v>0.48060378253189467</v>
+        <v>0.48060377976172758</v>
       </c>
       <c r="K2">
-        <v>0.4586448263593072</v>
+        <v>0.45864482352981212</v>
       </c>
       <c r="L2">
-        <v>0.46947524655997558</v>
+        <v>0.4694752427706374</v>
       </c>
       <c r="M2">
-        <v>0.45722070470630122</v>
+        <v>0.45722070209966492</v>
       </c>
       <c r="N2">
-        <v>0.43452404954275958</v>
+        <v>0.43452404846843418</v>
       </c>
       <c r="O2">
-        <v>0.4247318496996772</v>
+        <v>0.42473184523476909</v>
       </c>
       <c r="P2">
-        <v>0.40144362173557491</v>
+        <v>0.40144361505987303</v>
       </c>
       <c r="Q2">
-        <v>0.37787961633011091</v>
+        <v>0.37787960626080641</v>
       </c>
       <c r="R2">
-        <v>0.36580497996368488</v>
+        <v>0.36580496695833542</v>
       </c>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.25">
@@ -676,55 +676,55 @@
         <v>19</v>
       </c>
       <c r="B3">
-        <v>0.4371841300768296</v>
+        <v>0.43718412788660332</v>
       </c>
       <c r="C3">
-        <v>0.48594555921399668</v>
+        <v>0.48594555869191192</v>
       </c>
       <c r="D3">
-        <v>0.48693007513739578</v>
+        <v>0.48693007459908128</v>
       </c>
       <c r="E3">
-        <v>0.49234430812624719</v>
+        <v>0.49234430637081888</v>
       </c>
       <c r="F3">
-        <v>0.52209718826700713</v>
+        <v>0.52209719079758776</v>
       </c>
       <c r="G3">
-        <v>0.47808825727616638</v>
+        <v>0.47808826048960529</v>
       </c>
       <c r="H3">
-        <v>0.45627951564534258</v>
+        <v>0.45627951591012772</v>
       </c>
       <c r="I3">
-        <v>0.43841114400527947</v>
+        <v>0.43841114436114348</v>
       </c>
       <c r="J3">
-        <v>0.42434008656274602</v>
+        <v>0.424340103020792</v>
       </c>
       <c r="K3">
-        <v>0.41992371786066629</v>
+        <v>0.41992372344314549</v>
       </c>
       <c r="L3">
-        <v>0.40261697582974082</v>
+        <v>0.40261697622508841</v>
       </c>
       <c r="M3">
-        <v>0.38976389180599308</v>
+        <v>0.389763887669274</v>
       </c>
       <c r="N3">
-        <v>0.39080430403228661</v>
+        <v>0.39080429339816408</v>
       </c>
       <c r="O3">
-        <v>0.38896976020995699</v>
+        <v>0.38896973717715472</v>
       </c>
       <c r="P3">
-        <v>0.39851132582487903</v>
+        <v>0.39851128298908473</v>
       </c>
       <c r="Q3">
-        <v>0.40002804347199222</v>
+        <v>0.40002797364298393</v>
       </c>
       <c r="R3">
-        <v>0.39124743013102831</v>
+        <v>0.39124733793749589</v>
       </c>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.25">
@@ -732,55 +732,55 @@
         <v>20</v>
       </c>
       <c r="B4">
-        <v>0.4265484658251012</v>
+        <v>0.42654845838422673</v>
       </c>
       <c r="C4">
-        <v>0.48594555921399668</v>
+        <v>0.48594555869191192</v>
       </c>
       <c r="D4">
-        <v>0.4887279150808983</v>
+        <v>0.48872791390536119</v>
       </c>
       <c r="E4">
-        <v>0.49245718756941748</v>
+        <v>0.49245716951728991</v>
       </c>
       <c r="F4">
-        <v>0.51222723010393378</v>
+        <v>0.51222722819603927</v>
       </c>
       <c r="G4">
-        <v>0.5127307783848063</v>
+        <v>0.51273077327719374</v>
       </c>
       <c r="H4">
-        <v>0.52836909810507371</v>
+        <v>0.52836909826535816</v>
       </c>
       <c r="I4">
-        <v>0.49587054899704591</v>
+        <v>0.49587054013581161</v>
       </c>
       <c r="J4">
-        <v>0.45939021333486307</v>
+        <v>0.45939020420055299</v>
       </c>
       <c r="K4">
-        <v>0.45342733203679259</v>
+        <v>0.45342732604304792</v>
       </c>
       <c r="L4">
-        <v>0.44936805043665429</v>
+        <v>0.44936804338276382</v>
       </c>
       <c r="M4">
-        <v>0.4292430554837196</v>
+        <v>0.42924304852288941</v>
       </c>
       <c r="N4">
-        <v>0.41001135216232298</v>
+        <v>0.41001134440075337</v>
       </c>
       <c r="O4">
-        <v>0.39278834158983528</v>
+        <v>0.39278833324782469</v>
       </c>
       <c r="P4">
-        <v>0.38141044296596638</v>
+        <v>0.38141043331846169</v>
       </c>
       <c r="Q4">
-        <v>0.37744566342548008</v>
+        <v>0.37744565528046742</v>
       </c>
       <c r="R4">
-        <v>0.37946104239979228</v>
+        <v>0.3794610339577667</v>
       </c>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.25">
@@ -788,55 +788,55 @@
         <v>21</v>
       </c>
       <c r="B5">
-        <v>0.39745522524434701</v>
+        <v>0.39745522192963167</v>
       </c>
       <c r="C5">
-        <v>0.48594555921399668</v>
+        <v>0.48594555869191192</v>
       </c>
       <c r="D5">
-        <v>0.48755636714605632</v>
+        <v>0.48755636622047183</v>
       </c>
       <c r="E5">
-        <v>0.49926180815580612</v>
+        <v>0.4992618086760946</v>
       </c>
       <c r="F5">
-        <v>0.50173637327541654</v>
+        <v>0.50173637066682109</v>
       </c>
       <c r="G5">
-        <v>0.51252228512701281</v>
+        <v>0.51252228408494738</v>
       </c>
       <c r="H5">
-        <v>0.46017539656023693</v>
+        <v>0.46017539526347218</v>
       </c>
       <c r="I5">
-        <v>0.43561440855788108</v>
+        <v>0.4356144051486891</v>
       </c>
       <c r="J5">
-        <v>0.42167006606136198</v>
+        <v>0.42167006434232851</v>
       </c>
       <c r="K5">
-        <v>0.40312028272063499</v>
+        <v>0.40312027612868379</v>
       </c>
       <c r="L5">
-        <v>0.38189270953555338</v>
+        <v>0.38189270699110572</v>
       </c>
       <c r="M5">
-        <v>0.37030939516751959</v>
+        <v>0.37030938519435153</v>
       </c>
       <c r="N5">
-        <v>0.35753367984825313</v>
+        <v>0.35753366434694173</v>
       </c>
       <c r="O5">
-        <v>0.35771727660731462</v>
+        <v>0.3577172535865219</v>
       </c>
       <c r="P5">
-        <v>0.3644125221427777</v>
+        <v>0.36441249691854821</v>
       </c>
       <c r="Q5">
-        <v>0.37199919475905902</v>
+        <v>0.37199916503558927</v>
       </c>
       <c r="R5">
-        <v>0.37887044019806337</v>
+        <v>0.37887040068106659</v>
       </c>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.25">
@@ -844,55 +844,55 @@
         <v>22</v>
       </c>
       <c r="B6">
-        <v>0.3758144351961572</v>
+        <v>0.3758144300292674</v>
       </c>
       <c r="C6">
-        <v>0.48594555921399668</v>
+        <v>0.48594555869191192</v>
       </c>
       <c r="D6">
-        <v>0.4876195117684492</v>
+        <v>0.48761951086036309</v>
       </c>
       <c r="E6">
-        <v>0.49943738837591339</v>
+        <v>0.49943739018435512</v>
       </c>
       <c r="F6">
-        <v>0.50159338472441772</v>
+        <v>0.50159338278896726</v>
       </c>
       <c r="G6">
-        <v>0.49765582273427961</v>
+        <v>0.49765582589006341</v>
       </c>
       <c r="H6">
-        <v>0.43930224128583001</v>
+        <v>0.43930224099710208</v>
       </c>
       <c r="I6">
-        <v>0.4062477587801826</v>
+        <v>0.4062477531605006</v>
       </c>
       <c r="J6">
-        <v>0.39184879690863861</v>
+        <v>0.39184879431173281</v>
       </c>
       <c r="K6">
-        <v>0.36996165771130352</v>
+        <v>0.3699616521905798</v>
       </c>
       <c r="L6">
-        <v>0.3556679492582453</v>
+        <v>0.35566793970291088</v>
       </c>
       <c r="M6">
-        <v>0.34926949251305961</v>
+        <v>0.34926948413705061</v>
       </c>
       <c r="N6">
-        <v>0.34287488244209052</v>
+        <v>0.34287487302364489</v>
       </c>
       <c r="O6">
-        <v>0.34067418299801389</v>
+        <v>0.340674171633292</v>
       </c>
       <c r="P6">
-        <v>0.34346910650294998</v>
+        <v>0.34346909201960107</v>
       </c>
       <c r="Q6">
-        <v>0.34195064315898188</v>
+        <v>0.34195062587056702</v>
       </c>
       <c r="R6">
-        <v>0.34763702668618501</v>
+        <v>0.34763701008791043</v>
       </c>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.25">
@@ -900,55 +900,55 @@
         <v>23</v>
       </c>
       <c r="B7">
-        <v>0.42639350381070362</v>
+        <v>0.42639349418019451</v>
       </c>
       <c r="C7">
-        <v>0.48594555921399668</v>
+        <v>0.48594555869191192</v>
       </c>
       <c r="D7">
-        <v>0.48985574931640458</v>
+        <v>0.48985574818036992</v>
       </c>
       <c r="E7">
-        <v>0.49350061056118039</v>
+        <v>0.49350060948429619</v>
       </c>
       <c r="F7">
-        <v>0.51396064326894619</v>
+        <v>0.51396063998626373</v>
       </c>
       <c r="G7">
-        <v>0.51672936153378179</v>
+        <v>0.51672935661206387</v>
       </c>
       <c r="H7">
-        <v>0.52700061358016392</v>
+        <v>0.52700061482188398</v>
       </c>
       <c r="I7">
-        <v>0.52663239989754962</v>
+        <v>0.52663240079928553</v>
       </c>
       <c r="J7">
-        <v>0.49020783144325908</v>
+        <v>0.49020784404431789</v>
       </c>
       <c r="K7">
-        <v>0.4602840704059955</v>
+        <v>0.4602840684974252</v>
       </c>
       <c r="L7">
-        <v>0.46045659973140768</v>
+        <v>0.4604565917701185</v>
       </c>
       <c r="M7">
-        <v>0.44777444692530638</v>
+        <v>0.44777444061430183</v>
       </c>
       <c r="N7">
-        <v>0.42476728662181662</v>
+        <v>0.42476727694710831</v>
       </c>
       <c r="O7">
-        <v>0.4036194213400261</v>
+        <v>0.40361940984829148</v>
       </c>
       <c r="P7">
-        <v>0.38666363369745621</v>
+        <v>0.38666362310002522</v>
       </c>
       <c r="Q7">
-        <v>0.37614383423999731</v>
+        <v>0.37614382233417581</v>
       </c>
       <c r="R7">
-        <v>0.37158739716006078</v>
+        <v>0.37158738537437991</v>
       </c>
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.25">
@@ -956,55 +956,55 @@
         <v>24</v>
       </c>
       <c r="B8">
-        <v>0.41387947892573229</v>
+        <v>0.41387947324522628</v>
       </c>
       <c r="C8">
-        <v>0.48594555921399668</v>
+        <v>0.48594555869191192</v>
       </c>
       <c r="D8">
-        <v>0.48876214825963221</v>
+        <v>0.48876214729139028</v>
       </c>
       <c r="E8">
-        <v>0.49217686033869013</v>
+        <v>0.49217685993238081</v>
       </c>
       <c r="F8">
-        <v>0.50950008272538494</v>
+        <v>0.5095000802167442</v>
       </c>
       <c r="G8">
-        <v>0.51520482409924384</v>
+        <v>0.51520482353027774</v>
       </c>
       <c r="H8">
-        <v>0.50224966005789295</v>
+        <v>0.50224965441852565</v>
       </c>
       <c r="I8">
-        <v>0.48015004486971502</v>
+        <v>0.48015004058401117</v>
       </c>
       <c r="J8">
-        <v>0.4661736316489315</v>
+        <v>0.46617362043863242</v>
       </c>
       <c r="K8">
-        <v>0.44235129961232078</v>
+        <v>0.44235129528761519</v>
       </c>
       <c r="L8">
-        <v>0.4310709117663139</v>
+        <v>0.43107090703877349</v>
       </c>
       <c r="M8">
-        <v>0.39762185648146242</v>
+        <v>0.39762184723623478</v>
       </c>
       <c r="N8">
-        <v>0.39694677385277938</v>
+        <v>0.39694676384142369</v>
       </c>
       <c r="O8">
-        <v>0.38236634543048481</v>
+        <v>0.38236633574754308</v>
       </c>
       <c r="P8">
-        <v>0.37037635119104761</v>
+        <v>0.37037634077757481</v>
       </c>
       <c r="Q8">
-        <v>0.37067230457582051</v>
+        <v>0.37067229412677372</v>
       </c>
       <c r="R8">
-        <v>0.37213497626246411</v>
+        <v>0.37213496218809922</v>
       </c>
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.25">
@@ -1012,55 +1012,55 @@
         <v>25</v>
       </c>
       <c r="B9">
-        <v>0.38757925160500439</v>
+        <v>0.38757924627414381</v>
       </c>
       <c r="C9">
-        <v>0.48594555921399668</v>
+        <v>0.48594555869191192</v>
       </c>
       <c r="D9">
-        <v>0.4882154350120973</v>
+        <v>0.48821543406845941</v>
       </c>
       <c r="E9">
-        <v>0.49190836444041619</v>
+        <v>0.49190836363055468</v>
       </c>
       <c r="F9">
-        <v>0.507507817299922</v>
+        <v>0.50750781405679479</v>
       </c>
       <c r="G9">
-        <v>0.51362201501148208</v>
+        <v>0.51362201491191317</v>
       </c>
       <c r="H9">
-        <v>0.50021150711931506</v>
+        <v>0.50021150384900059</v>
       </c>
       <c r="I9">
-        <v>0.47844321883056462</v>
+        <v>0.47844321465822037</v>
       </c>
       <c r="J9">
-        <v>0.46573956492564872</v>
+        <v>0.46573956287301532</v>
       </c>
       <c r="K9">
-        <v>0.44222210850813631</v>
+        <v>0.44222210372872622</v>
       </c>
       <c r="L9">
-        <v>0.43085783488759438</v>
+        <v>0.43085782790173027</v>
       </c>
       <c r="M9">
-        <v>0.38371096051455589</v>
+        <v>0.38371095463379667</v>
       </c>
       <c r="N9">
-        <v>0.38133077608557181</v>
+        <v>0.38133077136284649</v>
       </c>
       <c r="O9">
-        <v>0.37014129065588047</v>
+        <v>0.37014128460350493</v>
       </c>
       <c r="P9">
-        <v>0.35908419919840051</v>
+        <v>0.35908419365831601</v>
       </c>
       <c r="Q9">
-        <v>0.35563641968890097</v>
+        <v>0.35563641748440072</v>
       </c>
       <c r="R9">
-        <v>0.35536721674708949</v>
+        <v>0.35536721510394309</v>
       </c>
     </row>
     <row r="10" spans="1:18" x14ac:dyDescent="0.25">
@@ -1068,55 +1068,55 @@
         <v>26</v>
       </c>
       <c r="B10">
-        <v>0.39364474379292302</v>
+        <v>0.39364473814638667</v>
       </c>
       <c r="C10">
-        <v>0.48594555921399668</v>
+        <v>0.48594555869191192</v>
       </c>
       <c r="D10">
-        <v>0.48782123876697092</v>
+        <v>0.48782123786193449</v>
       </c>
       <c r="E10">
-        <v>0.49140228515904361</v>
+        <v>0.49140228409643472</v>
       </c>
       <c r="F10">
-        <v>0.50951380451537154</v>
+        <v>0.50951380123140122</v>
       </c>
       <c r="G10">
-        <v>0.51405537981297766</v>
+        <v>0.5140553793544782</v>
       </c>
       <c r="H10">
-        <v>0.50227223690886025</v>
+        <v>0.50227223273833355</v>
       </c>
       <c r="I10">
-        <v>0.48035667811901922</v>
+        <v>0.48035667332151921</v>
       </c>
       <c r="J10">
-        <v>0.46613205299469151</v>
+        <v>0.46613204951339349</v>
       </c>
       <c r="K10">
-        <v>0.44274019427345679</v>
+        <v>0.44274018772121287</v>
       </c>
       <c r="L10">
-        <v>0.43312759477384022</v>
+        <v>0.43312758677605229</v>
       </c>
       <c r="M10">
-        <v>0.3877263198932589</v>
+        <v>0.38772631309212158</v>
       </c>
       <c r="N10">
-        <v>0.3865239865384722</v>
+        <v>0.38652398146969058</v>
       </c>
       <c r="O10">
-        <v>0.37536901918126608</v>
+        <v>0.37536901399607808</v>
       </c>
       <c r="P10">
-        <v>0.36577820602566108</v>
+        <v>0.36577820046673792</v>
       </c>
       <c r="Q10">
-        <v>0.36215702117807042</v>
+        <v>0.36215701854446403</v>
       </c>
       <c r="R10">
-        <v>0.36062969117831822</v>
+        <v>0.36062968655558852</v>
       </c>
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.25">
@@ -1124,55 +1124,55 @@
         <v>27</v>
       </c>
       <c r="B11">
-        <v>0.38884906665697871</v>
+        <v>0.38884905923797147</v>
       </c>
       <c r="C11">
-        <v>0.48594555921399668</v>
+        <v>0.48594555869191192</v>
       </c>
       <c r="D11">
-        <v>0.48901373128614628</v>
+        <v>0.4890137304370793</v>
       </c>
       <c r="E11">
-        <v>0.49290653765833869</v>
+        <v>0.49290653680817792</v>
       </c>
       <c r="F11">
-        <v>0.50916115347444191</v>
+        <v>0.50916115023997521</v>
       </c>
       <c r="G11">
-        <v>0.51483230157151905</v>
+        <v>0.51483230094236865</v>
       </c>
       <c r="H11">
-        <v>0.50174759602858654</v>
+        <v>0.50174759069760622</v>
       </c>
       <c r="I11">
-        <v>0.48093501802019989</v>
+        <v>0.48093501572535741</v>
       </c>
       <c r="J11">
-        <v>0.46843057249887549</v>
+        <v>0.46843057264141957</v>
       </c>
       <c r="K11">
-        <v>0.44124696033102989</v>
+        <v>0.44124695390244162</v>
       </c>
       <c r="L11">
-        <v>0.43055742342171072</v>
+        <v>0.43055741320429303</v>
       </c>
       <c r="M11">
-        <v>0.38334103621729698</v>
+        <v>0.38334103657372742</v>
       </c>
       <c r="N11">
-        <v>0.38029935117437219</v>
+        <v>0.38029934605688448</v>
       </c>
       <c r="O11">
-        <v>0.3693065556607229</v>
+        <v>0.36930654738821211</v>
       </c>
       <c r="P11">
-        <v>0.35940793444064079</v>
+        <v>0.35940792642947939</v>
       </c>
       <c r="Q11">
-        <v>0.35833860565052239</v>
+        <v>0.358338599587948</v>
       </c>
       <c r="R11">
-        <v>0.35711197263987071</v>
+        <v>0.35711195501044202</v>
       </c>
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.25">
@@ -1180,55 +1180,55 @@
         <v>28</v>
       </c>
       <c r="B12">
-        <v>0.38646480563156649</v>
+        <v>0.38646479564280078</v>
       </c>
       <c r="C12">
-        <v>0.48594555921399668</v>
+        <v>0.48594555869191192</v>
       </c>
       <c r="D12">
-        <v>0.48783329782282708</v>
+        <v>0.48783329690049537</v>
       </c>
       <c r="E12">
-        <v>0.50084869624457606</v>
+        <v>0.50084869696532175</v>
       </c>
       <c r="F12">
-        <v>0.49574144298315681</v>
+        <v>0.4957414404999807</v>
       </c>
       <c r="G12">
-        <v>0.50770127734391268</v>
+        <v>0.50770127755433314</v>
       </c>
       <c r="H12">
-        <v>0.46087900506055768</v>
+        <v>0.46087900609843602</v>
       </c>
       <c r="I12">
-        <v>0.44059078651450517</v>
+        <v>0.44059078212792679</v>
       </c>
       <c r="J12">
-        <v>0.41325800473117269</v>
+        <v>0.41325800096646959</v>
       </c>
       <c r="K12">
-        <v>0.38618551850338728</v>
+        <v>0.38618550843996963</v>
       </c>
       <c r="L12">
-        <v>0.37214742482831031</v>
+        <v>0.37214741317595268</v>
       </c>
       <c r="M12">
-        <v>0.36366203257066138</v>
+        <v>0.36366202096872341</v>
       </c>
       <c r="N12">
-        <v>0.35124928265076882</v>
+        <v>0.35124926253588867</v>
       </c>
       <c r="O12">
-        <v>0.35024354674875102</v>
+        <v>0.35024352348330418</v>
       </c>
       <c r="P12">
-        <v>0.35491355436373512</v>
+        <v>0.35491352561181599</v>
       </c>
       <c r="Q12">
-        <v>0.36253351487236768</v>
+        <v>0.36253348201596342</v>
       </c>
       <c r="R12">
-        <v>0.37468280639143559</v>
+        <v>0.37468276036485082</v>
       </c>
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.25">
@@ -1236,55 +1236,55 @@
         <v>29</v>
       </c>
       <c r="B13">
-        <v>0.46320966441865091</v>
+        <v>0.46320965667876468</v>
       </c>
       <c r="C13">
-        <v>0.48594555921399668</v>
+        <v>0.48594555869191192</v>
       </c>
       <c r="D13">
-        <v>0.48715502804578559</v>
+        <v>0.48715502718360482</v>
       </c>
       <c r="E13">
-        <v>0.50946714811057392</v>
+        <v>0.50946714886153721</v>
       </c>
       <c r="F13">
-        <v>0.50780664545863141</v>
+        <v>0.50780664310352941</v>
       </c>
       <c r="G13">
-        <v>0.51184398539278153</v>
+        <v>0.51184398780970697</v>
       </c>
       <c r="H13">
-        <v>0.51916661609536219</v>
+        <v>0.51916662223950261</v>
       </c>
       <c r="I13">
-        <v>0.4860202655700141</v>
+        <v>0.48602026834433742</v>
       </c>
       <c r="J13">
-        <v>0.48011129148669363</v>
+        <v>0.48011129397549901</v>
       </c>
       <c r="K13">
-        <v>0.46414965423944848</v>
+        <v>0.46414965644581863</v>
       </c>
       <c r="L13">
-        <v>0.44337908439014978</v>
+        <v>0.44337907690353029</v>
       </c>
       <c r="M13">
-        <v>0.42340724252104261</v>
+        <v>0.42340722876021841</v>
       </c>
       <c r="N13">
-        <v>0.41752970180877041</v>
+        <v>0.41752968502755677</v>
       </c>
       <c r="O13">
-        <v>0.41059397069112469</v>
+        <v>0.41059394740757499</v>
       </c>
       <c r="P13">
-        <v>0.40827852078386262</v>
+        <v>0.40827849074038758</v>
       </c>
       <c r="Q13">
-        <v>0.40480801808644601</v>
+        <v>0.40480797386453371</v>
       </c>
       <c r="R13">
-        <v>0.41061646623797993</v>
+        <v>0.41061641010542732</v>
       </c>
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.25">
@@ -1292,55 +1292,55 @@
         <v>30</v>
       </c>
       <c r="B14">
-        <v>0.39426573573478019</v>
+        <v>0.39426572879716859</v>
       </c>
       <c r="C14">
-        <v>0.48594555921399668</v>
+        <v>0.48594555869191192</v>
       </c>
       <c r="D14">
-        <v>0.48909082083059607</v>
+        <v>0.48909081943020222</v>
       </c>
       <c r="E14">
-        <v>0.49331380709757172</v>
+        <v>0.49331380538891328</v>
       </c>
       <c r="F14">
-        <v>0.51294426645951474</v>
+        <v>0.5129442637958781</v>
       </c>
       <c r="G14">
-        <v>0.51350552962535934</v>
+        <v>0.51350552454740328</v>
       </c>
       <c r="H14">
-        <v>0.52342171237403323</v>
+        <v>0.52342171094665191</v>
       </c>
       <c r="I14">
-        <v>0.52106949628972099</v>
+        <v>0.52106949621207188</v>
       </c>
       <c r="J14">
-        <v>0.48756789744499668</v>
+        <v>0.48756789344263191</v>
       </c>
       <c r="K14">
-        <v>0.4578847276714208</v>
+        <v>0.45788472229766958</v>
       </c>
       <c r="L14">
-        <v>0.45706661297676981</v>
+        <v>0.45706660583912501</v>
       </c>
       <c r="M14">
-        <v>0.44747736576775188</v>
+        <v>0.44747735740329397</v>
       </c>
       <c r="N14">
-        <v>0.41892761228226733</v>
+        <v>0.41892760071365742</v>
       </c>
       <c r="O14">
-        <v>0.38730347423556422</v>
+        <v>0.38730346678665739</v>
       </c>
       <c r="P14">
-        <v>0.37508676949999448</v>
+        <v>0.37508676120849738</v>
       </c>
       <c r="Q14">
-        <v>0.36586610666184199</v>
+        <v>0.36586609643726198</v>
       </c>
       <c r="R14">
-        <v>0.36088746776451019</v>
+        <v>0.36088745814276169</v>
       </c>
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.25">
@@ -1348,55 +1348,55 @@
         <v>31</v>
       </c>
       <c r="B15">
-        <v>0.40225304572761611</v>
+        <v>0.40225303927614731</v>
       </c>
       <c r="C15">
-        <v>0.48594555921399668</v>
+        <v>0.48594555869191192</v>
       </c>
       <c r="D15">
-        <v>0.4891360160101717</v>
+        <v>0.48913601473345331</v>
       </c>
       <c r="E15">
-        <v>0.49254749610802312</v>
+        <v>0.49254749527994929</v>
       </c>
       <c r="F15">
-        <v>0.51179711127637761</v>
+        <v>0.51179710823268765</v>
       </c>
       <c r="G15">
-        <v>0.51264142786705746</v>
+        <v>0.51264142318870465</v>
       </c>
       <c r="H15">
-        <v>0.52138132354845568</v>
+        <v>0.52138132097429124</v>
       </c>
       <c r="I15">
-        <v>0.51881024557971533</v>
+        <v>0.51881024071906812</v>
       </c>
       <c r="J15">
-        <v>0.48710925543105399</v>
+        <v>0.48710933896285807</v>
       </c>
       <c r="K15">
-        <v>0.46036010029314978</v>
+        <v>0.46036028009195518</v>
       </c>
       <c r="L15">
-        <v>0.45909358678196133</v>
+        <v>0.45909357603519951</v>
       </c>
       <c r="M15">
-        <v>0.44737243452525022</v>
+        <v>0.44737242180854342</v>
       </c>
       <c r="N15">
-        <v>0.42292889035933451</v>
+        <v>0.42292888125095562</v>
       </c>
       <c r="O15">
-        <v>0.39303209675486078</v>
+        <v>0.39303208913517518</v>
       </c>
       <c r="P15">
-        <v>0.37984964148238431</v>
+        <v>0.37984963439841268</v>
       </c>
       <c r="Q15">
-        <v>0.369396498510078</v>
+        <v>0.36939648837968292</v>
       </c>
       <c r="R15">
-        <v>0.36453111915687958</v>
+        <v>0.36453111139982652</v>
       </c>
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.25">
@@ -1404,55 +1404,55 @@
         <v>32</v>
       </c>
       <c r="B16">
-        <v>0.39719168161007562</v>
+        <v>0.39719167562527458</v>
       </c>
       <c r="C16">
-        <v>0.48594555921399668</v>
+        <v>0.48594555869191192</v>
       </c>
       <c r="D16">
-        <v>0.48911168532602889</v>
+        <v>0.48911168380087788</v>
       </c>
       <c r="E16">
-        <v>0.4930679587109788</v>
+        <v>0.49306795632266037</v>
       </c>
       <c r="F16">
-        <v>0.51224155285113904</v>
+        <v>0.5122415496957089</v>
       </c>
       <c r="G16">
-        <v>0.51260037059345487</v>
+        <v>0.512600365101606</v>
       </c>
       <c r="H16">
-        <v>0.52316424972931486</v>
+        <v>0.52316424953553953</v>
       </c>
       <c r="I16">
-        <v>0.52009801256754529</v>
+        <v>0.52009801009161927</v>
       </c>
       <c r="J16">
-        <v>0.48880698455290489</v>
+        <v>0.4888069814367238</v>
       </c>
       <c r="K16">
-        <v>0.4593268089288734</v>
+        <v>0.45932680320945579</v>
       </c>
       <c r="L16">
-        <v>0.4579838180565533</v>
+        <v>0.45798381174975911</v>
       </c>
       <c r="M16">
-        <v>0.44773658939098487</v>
+        <v>0.44773658146060341</v>
       </c>
       <c r="N16">
-        <v>0.4206971572982125</v>
+        <v>0.4206971498820099</v>
       </c>
       <c r="O16">
-        <v>0.38950485061243117</v>
+        <v>0.38950484441266697</v>
       </c>
       <c r="P16">
-        <v>0.37451999374486239</v>
+        <v>0.37451998723353958</v>
       </c>
       <c r="Q16">
-        <v>0.36484012638468438</v>
+        <v>0.36484011840604802</v>
       </c>
       <c r="R16">
-        <v>0.35846925441534772</v>
+        <v>0.3584692487371795</v>
       </c>
     </row>
     <row r="17" spans="1:18" x14ac:dyDescent="0.25">
@@ -1460,55 +1460,55 @@
         <v>33</v>
       </c>
       <c r="B17">
-        <v>0.40938775038778902</v>
+        <v>0.40938774679475848</v>
       </c>
       <c r="C17">
-        <v>0.48594555921399668</v>
+        <v>0.48594555869191192</v>
       </c>
       <c r="D17">
-        <v>0.49015415301697451</v>
+        <v>0.49015415170874199</v>
       </c>
       <c r="E17">
-        <v>0.49439227983013989</v>
+        <v>0.49439227946303582</v>
       </c>
       <c r="F17">
-        <v>0.51415244639709501</v>
+        <v>0.51415244344974065</v>
       </c>
       <c r="G17">
-        <v>0.51581316840275793</v>
+        <v>0.51581316302172386</v>
       </c>
       <c r="H17">
-        <v>0.52471145680574249</v>
+        <v>0.52471145565519617</v>
       </c>
       <c r="I17">
-        <v>0.52197484136113825</v>
+        <v>0.52197483896541974</v>
       </c>
       <c r="J17">
-        <v>0.49073068685748189</v>
+        <v>0.49073068123049579</v>
       </c>
       <c r="K17">
-        <v>0.46438703943827531</v>
+        <v>0.46438703302427697</v>
       </c>
       <c r="L17">
-        <v>0.4650555899639211</v>
+        <v>0.46505558369937272</v>
       </c>
       <c r="M17">
-        <v>0.45506445184160199</v>
+        <v>0.45506444554228331</v>
       </c>
       <c r="N17">
-        <v>0.43200190859196308</v>
+        <v>0.43200190747507999</v>
       </c>
       <c r="O17">
-        <v>0.40138541185117388</v>
+        <v>0.40138540449218629</v>
       </c>
       <c r="P17">
-        <v>0.38796959576249851</v>
+        <v>0.38796958881639593</v>
       </c>
       <c r="Q17">
-        <v>0.37523835138458272</v>
+        <v>0.3752383420961572</v>
       </c>
       <c r="R17">
-        <v>0.36728913148177611</v>
+        <v>0.36728912310081852</v>
       </c>
     </row>
     <row r="18" spans="1:18" x14ac:dyDescent="0.25">
@@ -1516,55 +1516,55 @@
         <v>34</v>
       </c>
       <c r="B18">
-        <v>0.38571122911366967</v>
+        <v>0.38571122127997648</v>
       </c>
       <c r="C18">
-        <v>0.48594555921399668</v>
+        <v>0.48594555869191192</v>
       </c>
       <c r="D18">
-        <v>0.48712109902383161</v>
+        <v>0.48712109806897319</v>
       </c>
       <c r="E18">
-        <v>0.5000051006374735</v>
+        <v>0.50000510148231436</v>
       </c>
       <c r="F18">
-        <v>0.50193884353679319</v>
+        <v>0.50193884333937033</v>
       </c>
       <c r="G18">
-        <v>0.51286751019642263</v>
+        <v>0.51286751003858444</v>
       </c>
       <c r="H18">
-        <v>0.46380728393960302</v>
+        <v>0.46380728061464299</v>
       </c>
       <c r="I18">
-        <v>0.43293195206014629</v>
+        <v>0.43293194872240198</v>
       </c>
       <c r="J18">
-        <v>0.41608300521560332</v>
+        <v>0.41608300233922918</v>
       </c>
       <c r="K18">
-        <v>0.39082015330248132</v>
+        <v>0.39082014660804909</v>
       </c>
       <c r="L18">
-        <v>0.3707911263570442</v>
+        <v>0.37079112022027427</v>
       </c>
       <c r="M18">
-        <v>0.36496833500904502</v>
+        <v>0.36496834756962299</v>
       </c>
       <c r="N18">
-        <v>0.35319325504247551</v>
+        <v>0.35319323706449579</v>
       </c>
       <c r="O18">
-        <v>0.35283613171208861</v>
+        <v>0.35283611150261679</v>
       </c>
       <c r="P18">
-        <v>0.36038505978024798</v>
+        <v>0.36038503536738681</v>
       </c>
       <c r="Q18">
-        <v>0.37032900277356418</v>
+        <v>0.37032897446994922</v>
       </c>
       <c r="R18">
-        <v>0.37464432429063721</v>
+        <v>0.37464428640918651</v>
       </c>
     </row>
     <row r="19" spans="1:18" x14ac:dyDescent="0.25">
@@ -1572,55 +1572,55 @@
         <v>35</v>
       </c>
       <c r="B19">
-        <v>0.38214204584498229</v>
+        <v>0.38214204088911791</v>
       </c>
       <c r="C19">
-        <v>0.48594555921399668</v>
+        <v>0.48594555869191192</v>
       </c>
       <c r="D19">
-        <v>0.48720312438578028</v>
+        <v>0.4872031234156875</v>
       </c>
       <c r="E19">
-        <v>0.49977994028783218</v>
+        <v>0.49977994164686851</v>
       </c>
       <c r="F19">
-        <v>0.50359162197650531</v>
+        <v>0.50359161639529471</v>
       </c>
       <c r="G19">
-        <v>0.50506133861577363</v>
+        <v>0.50506133933278019</v>
       </c>
       <c r="H19">
-        <v>0.44852924319062187</v>
+        <v>0.44852924043990872</v>
       </c>
       <c r="I19">
-        <v>0.41251036484308828</v>
+        <v>0.41251036065244329</v>
       </c>
       <c r="J19">
-        <v>0.3995381539033474</v>
+        <v>0.39953814911488122</v>
       </c>
       <c r="K19">
-        <v>0.37540463258144668</v>
+        <v>0.37540462707255923</v>
       </c>
       <c r="L19">
-        <v>0.36035302096348237</v>
+        <v>0.36035301218622617</v>
       </c>
       <c r="M19">
-        <v>0.35507456569155083</v>
+        <v>0.35507460529862311</v>
       </c>
       <c r="N19">
-        <v>0.34774889037667861</v>
+        <v>0.34774888144490329</v>
       </c>
       <c r="O19">
-        <v>0.34690132419107472</v>
+        <v>0.34690131379264028</v>
       </c>
       <c r="P19">
-        <v>0.34921365867251292</v>
+        <v>0.34921364726943599</v>
       </c>
       <c r="Q19">
-        <v>0.34675497691429741</v>
+        <v>0.34675496127429117</v>
       </c>
       <c r="R19">
-        <v>0.34876387694606992</v>
+        <v>0.3487638543990409</v>
       </c>
     </row>
     <row r="20" spans="1:18" x14ac:dyDescent="0.25">
@@ -1628,55 +1628,55 @@
         <v>36</v>
       </c>
       <c r="B20">
-        <v>0.37551046554323381</v>
+        <v>0.37551045084276208</v>
       </c>
       <c r="C20">
-        <v>0.48594555921399668</v>
+        <v>0.48594555869191192</v>
       </c>
       <c r="D20">
-        <v>0.48746894815545888</v>
+        <v>0.48746894713223882</v>
       </c>
       <c r="E20">
-        <v>0.49731500890112551</v>
+        <v>0.4973150106726793</v>
       </c>
       <c r="F20">
-        <v>0.50143733893693343</v>
+        <v>0.50143733769528787</v>
       </c>
       <c r="G20">
-        <v>0.47883892194393612</v>
+        <v>0.47883892094549702</v>
       </c>
       <c r="H20">
-        <v>0.43938253546396722</v>
+        <v>0.43938253292612611</v>
       </c>
       <c r="I20">
-        <v>0.43011875825750678</v>
+        <v>0.4301187535699495</v>
       </c>
       <c r="J20">
-        <v>0.4000811353698322</v>
+        <v>0.4000811290897559</v>
       </c>
       <c r="K20">
-        <v>0.37856017317553109</v>
+        <v>0.37856016780275858</v>
       </c>
       <c r="L20">
-        <v>0.3685543436191091</v>
+        <v>0.3685543041129819</v>
       </c>
       <c r="M20">
-        <v>0.35081711638328977</v>
+        <v>0.35081710354308371</v>
       </c>
       <c r="N20">
-        <v>0.34507386481663782</v>
+        <v>0.34507385775079158</v>
       </c>
       <c r="O20">
-        <v>0.35048610115543261</v>
+        <v>0.35048609487118931</v>
       </c>
       <c r="P20">
-        <v>0.33361650387502573</v>
+        <v>0.33361649316294772</v>
       </c>
       <c r="Q20">
-        <v>0.33635450068294293</v>
+        <v>0.33635448426594899</v>
       </c>
       <c r="R20">
-        <v>0.3379979382747163</v>
+        <v>0.33799792532659961</v>
       </c>
     </row>
     <row r="21" spans="1:18" x14ac:dyDescent="0.25">
@@ -1684,55 +1684,55 @@
         <v>37</v>
       </c>
       <c r="B21">
-        <v>0.43434065960212731</v>
+        <v>0.43434065232158142</v>
       </c>
       <c r="C21">
-        <v>0.48594555921399668</v>
+        <v>0.48594555869191192</v>
       </c>
       <c r="D21">
-        <v>0.48649930624382381</v>
+        <v>0.48649930551418419</v>
       </c>
       <c r="E21">
-        <v>0.4905968691329825</v>
+        <v>0.49059686788647783</v>
       </c>
       <c r="F21">
-        <v>0.51321579703134468</v>
+        <v>0.51321580025013525</v>
       </c>
       <c r="G21">
-        <v>0.47423506590125869</v>
+        <v>0.47423506714687419</v>
       </c>
       <c r="H21">
-        <v>0.45357315470192272</v>
+        <v>0.45357315696257589</v>
       </c>
       <c r="I21">
-        <v>0.44599359271177219</v>
+        <v>0.44599360134513072</v>
       </c>
       <c r="J21">
-        <v>0.43663237007772993</v>
+        <v>0.43663236927926768</v>
       </c>
       <c r="K21">
-        <v>0.42347697862149491</v>
+        <v>0.42347697142431923</v>
       </c>
       <c r="L21">
-        <v>0.40317831663427439</v>
+        <v>0.40317830812077521</v>
       </c>
       <c r="M21">
-        <v>0.39230699758791338</v>
+        <v>0.39230697921566537</v>
       </c>
       <c r="N21">
-        <v>0.38547256273374109</v>
+        <v>0.38547253188076269</v>
       </c>
       <c r="O21">
-        <v>0.3890510151476711</v>
+        <v>0.38905097098166791</v>
       </c>
       <c r="P21">
-        <v>0.39717891088670698</v>
+        <v>0.39717885581831369</v>
       </c>
       <c r="Q21">
-        <v>0.39925508125006859</v>
+        <v>0.39925499771984801</v>
       </c>
       <c r="R21">
-        <v>0.39764975560799248</v>
+        <v>0.39764965047254808</v>
       </c>
     </row>
     <row r="22" spans="1:18" x14ac:dyDescent="0.25">
@@ -1740,55 +1740,55 @@
         <v>38</v>
       </c>
       <c r="B22">
-        <v>0.45203959391939391</v>
+        <v>0.45203957681490292</v>
       </c>
       <c r="C22">
-        <v>0.48594555921399668</v>
+        <v>0.48594555869191192</v>
       </c>
       <c r="D22">
-        <v>0.48665555471799099</v>
+        <v>0.4866555540427932</v>
       </c>
       <c r="E22">
-        <v>0.491298054238268</v>
+        <v>0.49129805264720638</v>
       </c>
       <c r="F22">
-        <v>0.5139603526543699</v>
+        <v>0.51396035478691848</v>
       </c>
       <c r="G22">
-        <v>0.47349708993492601</v>
+        <v>0.47349709207633928</v>
       </c>
       <c r="H22">
-        <v>0.45659063054140231</v>
+        <v>0.45659063390360649</v>
       </c>
       <c r="I22">
-        <v>0.44982049643952893</v>
+        <v>0.44982049346353398</v>
       </c>
       <c r="J22">
-        <v>0.44216862645213351</v>
+        <v>0.44216861858901929</v>
       </c>
       <c r="K22">
-        <v>0.43551896080835151</v>
+        <v>0.43551894628582433</v>
       </c>
       <c r="L22">
-        <v>0.41380038501761712</v>
+        <v>0.41380036399826647</v>
       </c>
       <c r="M22">
-        <v>0.40276409165002558</v>
+        <v>0.40276406655863911</v>
       </c>
       <c r="N22">
-        <v>0.39690458016353419</v>
+        <v>0.39690454034187062</v>
       </c>
       <c r="O22">
-        <v>0.39732490338402121</v>
+        <v>0.39732484091998688</v>
       </c>
       <c r="P22">
-        <v>0.40009442063896511</v>
+        <v>0.40009432452480742</v>
       </c>
       <c r="Q22">
-        <v>0.39994639267154147</v>
+        <v>0.39994626939223538</v>
       </c>
       <c r="R22">
-        <v>0.40156531473617901</v>
+        <v>0.40156516657238478</v>
       </c>
     </row>
     <row r="23" spans="1:18" x14ac:dyDescent="0.25">
@@ -1796,55 +1796,55 @@
         <v>39</v>
       </c>
       <c r="B23">
-        <v>0.38684311063141641</v>
+        <v>0.38684310745954331</v>
       </c>
       <c r="C23">
-        <v>0.48594555921399668</v>
+        <v>0.48594555869191192</v>
       </c>
       <c r="D23">
-        <v>0.48641006007626009</v>
+        <v>0.48641005936616932</v>
       </c>
       <c r="E23">
-        <v>0.50255194622171784</v>
+        <v>0.5025519588730426</v>
       </c>
       <c r="F23">
-        <v>0.46716517125688389</v>
+        <v>0.46716518394357581</v>
       </c>
       <c r="G23">
-        <v>0.45483476525401467</v>
+        <v>0.45483477530257133</v>
       </c>
       <c r="H23">
-        <v>0.4077453216677896</v>
+        <v>0.40774532742691078</v>
       </c>
       <c r="I23">
-        <v>0.38206011588720729</v>
+        <v>0.38206011638941961</v>
       </c>
       <c r="J23">
-        <v>0.37027111353144371</v>
+        <v>0.37027110970414018</v>
       </c>
       <c r="K23">
-        <v>0.36015452088274208</v>
+        <v>0.36015450608704758</v>
       </c>
       <c r="L23">
-        <v>0.35179268756629872</v>
+        <v>0.35179266119591007</v>
       </c>
       <c r="M23">
-        <v>0.34831477714526382</v>
+        <v>0.34831472075114639</v>
       </c>
       <c r="N23">
-        <v>0.34807887759774098</v>
+        <v>0.34807879322085788</v>
       </c>
       <c r="O23">
-        <v>0.35524127854079218</v>
+        <v>0.35524114995298622</v>
       </c>
       <c r="P23">
-        <v>0.3611786889595503</v>
+        <v>0.36117853945863793</v>
       </c>
       <c r="Q23">
-        <v>0.36678142781348722</v>
+        <v>0.36678127089583862</v>
       </c>
       <c r="R23">
-        <v>0.37458118072150381</v>
+        <v>0.37458100451114429</v>
       </c>
     </row>
     <row r="24" spans="1:18" x14ac:dyDescent="0.25">
@@ -1852,55 +1852,55 @@
         <v>40</v>
       </c>
       <c r="B24">
-        <v>0.45670108643464991</v>
+        <v>0.45670107287750311</v>
       </c>
       <c r="C24">
-        <v>0.48594555921399668</v>
+        <v>0.48594555869191192</v>
       </c>
       <c r="D24">
-        <v>0.49084085590133492</v>
+        <v>0.49084085513375858</v>
       </c>
       <c r="E24">
-        <v>0.51345877487269043</v>
+        <v>0.51345877484122404</v>
       </c>
       <c r="F24">
-        <v>0.51721857221126921</v>
+        <v>0.51721856997490345</v>
       </c>
       <c r="G24">
-        <v>0.51077633512413068</v>
+        <v>0.51077633383101606</v>
       </c>
       <c r="H24">
-        <v>0.51221064385192561</v>
+        <v>0.51221064075853806</v>
       </c>
       <c r="I24">
-        <v>0.49557177641210631</v>
+        <v>0.49557177611268732</v>
       </c>
       <c r="J24">
-        <v>0.51067299154166479</v>
+        <v>0.5106729902749807</v>
       </c>
       <c r="K24">
-        <v>0.48967582619882072</v>
+        <v>0.48967581810034022</v>
       </c>
       <c r="L24">
-        <v>0.44117349952279822</v>
+        <v>0.4411734822367307</v>
       </c>
       <c r="M24">
-        <v>0.42342689939123779</v>
+        <v>0.42342687976036358</v>
       </c>
       <c r="N24">
-        <v>0.41325087404006111</v>
+        <v>0.41325084583123528</v>
       </c>
       <c r="O24">
-        <v>0.419353732307365</v>
+        <v>0.41935369270067457</v>
       </c>
       <c r="P24">
-        <v>0.4371730471141535</v>
+        <v>0.4371729881487203</v>
       </c>
       <c r="Q24">
-        <v>0.45040906262009389</v>
+        <v>0.45040900246086091</v>
       </c>
       <c r="R24">
-        <v>0.46692033756607199</v>
+        <v>0.4669202749641192</v>
       </c>
     </row>
     <row r="25" spans="1:18" x14ac:dyDescent="0.25">
@@ -1908,55 +1908,55 @@
         <v>41</v>
       </c>
       <c r="B25">
-        <v>0.46292553105899958</v>
+        <v>0.46292552083936178</v>
       </c>
       <c r="C25">
-        <v>0.48594555921399668</v>
+        <v>0.48594555869191192</v>
       </c>
       <c r="D25">
-        <v>0.4909172440776281</v>
+        <v>0.49091724280103488</v>
       </c>
       <c r="E25">
-        <v>0.51552829204001127</v>
+        <v>0.51552829400907429</v>
       </c>
       <c r="F25">
-        <v>0.5170112988978578</v>
+        <v>0.51701129808444102</v>
       </c>
       <c r="G25">
-        <v>0.50825812721050745</v>
+        <v>0.50825812554403116</v>
       </c>
       <c r="H25">
-        <v>0.50728782560199037</v>
+        <v>0.50728782983649912</v>
       </c>
       <c r="I25">
-        <v>0.50363016532486304</v>
+        <v>0.50363016413669259</v>
       </c>
       <c r="J25">
-        <v>0.51989461052946928</v>
+        <v>0.51989460840551438</v>
       </c>
       <c r="K25">
-        <v>0.51009626442061784</v>
+        <v>0.51009625851038742</v>
       </c>
       <c r="L25">
-        <v>0.49013716119695527</v>
+        <v>0.49013715325021678</v>
       </c>
       <c r="M25">
-        <v>0.4360107644005235</v>
+        <v>0.43601074863349581</v>
       </c>
       <c r="N25">
-        <v>0.42708482958390043</v>
+        <v>0.42708481084661309</v>
       </c>
       <c r="O25">
-        <v>0.41891227686980481</v>
+        <v>0.41891224321986908</v>
       </c>
       <c r="P25">
-        <v>0.42902420474469199</v>
+        <v>0.42902416900941431</v>
       </c>
       <c r="Q25">
-        <v>0.44214590277087018</v>
+        <v>0.44214580868698261</v>
       </c>
       <c r="R25">
-        <v>0.45845970228363692</v>
+        <v>0.45845963383867938</v>
       </c>
     </row>
     <row r="26" spans="1:18" x14ac:dyDescent="0.25">
@@ -1964,55 +1964,55 @@
         <v>42</v>
       </c>
       <c r="B26">
-        <v>0.4786279528763045</v>
+        <v>0.47862794806971332</v>
       </c>
       <c r="C26">
-        <v>0.48594555921399668</v>
+        <v>0.48594555869191192</v>
       </c>
       <c r="D26">
-        <v>0.4898144279153937</v>
+        <v>0.48981442694343841</v>
       </c>
       <c r="E26">
-        <v>0.51599420586704747</v>
+        <v>0.51599420568509224</v>
       </c>
       <c r="F26">
-        <v>0.51128512070217924</v>
+        <v>0.51128511984929792</v>
       </c>
       <c r="G26">
-        <v>0.50025646497664622</v>
+        <v>0.50025646437219007</v>
       </c>
       <c r="H26">
-        <v>0.50995449625790423</v>
+        <v>0.50995450679224119</v>
       </c>
       <c r="I26">
-        <v>0.50260912822016146</v>
+        <v>0.50260912624619092</v>
       </c>
       <c r="J26">
-        <v>0.47256909666798252</v>
+        <v>0.47256909220429938</v>
       </c>
       <c r="K26">
-        <v>0.48644632571732888</v>
+        <v>0.48644632095289669</v>
       </c>
       <c r="L26">
-        <v>0.45010823219807422</v>
+        <v>0.45010822142943402</v>
       </c>
       <c r="M26">
-        <v>0.42492224233635478</v>
+        <v>0.42492222560698001</v>
       </c>
       <c r="N26">
-        <v>0.42332909760507781</v>
+        <v>0.42332907289395078</v>
       </c>
       <c r="O26">
-        <v>0.43054999418000578</v>
+        <v>0.43054995046795791</v>
       </c>
       <c r="P26">
-        <v>0.44104811147467521</v>
+        <v>0.44104805806330788</v>
       </c>
       <c r="Q26">
-        <v>0.45416677251806759</v>
+        <v>0.45416670947591542</v>
       </c>
       <c r="R26">
-        <v>0.47396244400570048</v>
+        <v>0.47396237694877652</v>
       </c>
     </row>
     <row r="27" spans="1:18" x14ac:dyDescent="0.25">
@@ -2020,55 +2020,55 @@
         <v>43</v>
       </c>
       <c r="B27">
-        <v>0.43045241404720758</v>
+        <v>0.4304523982536731</v>
       </c>
       <c r="C27">
-        <v>0.48594555921399668</v>
+        <v>0.48594555869191192</v>
       </c>
       <c r="D27">
-        <v>0.49152318222970087</v>
+        <v>0.49152318070346518</v>
       </c>
       <c r="E27">
-        <v>0.51712216160679403</v>
+        <v>0.51712216059881844</v>
       </c>
       <c r="F27">
-        <v>0.51199770028545044</v>
+        <v>0.5119976990112689</v>
       </c>
       <c r="G27">
-        <v>0.50245388225549292</v>
+        <v>0.50245387931436558</v>
       </c>
       <c r="H27">
-        <v>0.510174480100408</v>
+        <v>0.51017447946150207</v>
       </c>
       <c r="I27">
-        <v>0.50353866348298382</v>
+        <v>0.50353866094610389</v>
       </c>
       <c r="J27">
-        <v>0.4772989297118666</v>
+        <v>0.4772989283818555</v>
       </c>
       <c r="K27">
-        <v>0.48742849737944832</v>
+        <v>0.48742849161418339</v>
       </c>
       <c r="L27">
-        <v>0.45489002696255909</v>
+        <v>0.45489002061356748</v>
       </c>
       <c r="M27">
-        <v>0.41344870113575238</v>
+        <v>0.41344868328915307</v>
       </c>
       <c r="N27">
-        <v>0.40339228042029618</v>
+        <v>0.4033922589223683</v>
       </c>
       <c r="O27">
-        <v>0.40133419542249538</v>
+        <v>0.40133416406006961</v>
       </c>
       <c r="P27">
-        <v>0.39838639721305152</v>
+        <v>0.39838636079699791</v>
       </c>
       <c r="Q27">
-        <v>0.40433435816753999</v>
+        <v>0.40433430782719321</v>
       </c>
       <c r="R27">
-        <v>0.40772676446344258</v>
+        <v>0.40772671303798902</v>
       </c>
     </row>
     <row r="28" spans="1:18" x14ac:dyDescent="0.25">
@@ -2076,55 +2076,55 @@
         <v>44</v>
       </c>
       <c r="B28">
-        <v>0.43423574797661779</v>
+        <v>0.43423573076663607</v>
       </c>
       <c r="C28">
-        <v>0.48594555921399668</v>
+        <v>0.48594555869191192</v>
       </c>
       <c r="D28">
-        <v>0.49045831879986868</v>
+        <v>0.49045831741188117</v>
       </c>
       <c r="E28">
-        <v>0.513635414085997</v>
+        <v>0.5136354144099472</v>
       </c>
       <c r="F28">
-        <v>0.51589101565095041</v>
+        <v>0.5158910136161432</v>
       </c>
       <c r="G28">
-        <v>0.50726596908348853</v>
+        <v>0.50726596707778426</v>
       </c>
       <c r="H28">
-        <v>0.50594369030665443</v>
+        <v>0.5059436918607414</v>
       </c>
       <c r="I28">
-        <v>0.5013718557118596</v>
+        <v>0.5013718556781761</v>
       </c>
       <c r="J28">
-        <v>0.51309959035175345</v>
+        <v>0.51309958942939127</v>
       </c>
       <c r="K28">
-        <v>0.50727419780884797</v>
+        <v>0.5072741940598402</v>
       </c>
       <c r="L28">
-        <v>0.4892539073006138</v>
+        <v>0.48925390079922632</v>
       </c>
       <c r="M28">
-        <v>0.43155938203771321</v>
+        <v>0.43155936541878759</v>
       </c>
       <c r="N28">
-        <v>0.41582130500402043</v>
+        <v>0.41582128377673733</v>
       </c>
       <c r="O28">
-        <v>0.41237240590702878</v>
+        <v>0.41237237974817598</v>
       </c>
       <c r="P28">
-        <v>0.41098568409237213</v>
+        <v>0.4109856534941897</v>
       </c>
       <c r="Q28">
-        <v>0.41686930362727281</v>
+        <v>0.41686926646424488</v>
       </c>
       <c r="R28">
-        <v>0.41629913972875809</v>
+        <v>0.41629909374093449</v>
       </c>
     </row>
     <row r="29" spans="1:18" x14ac:dyDescent="0.25">
@@ -2132,55 +2132,55 @@
         <v>45</v>
       </c>
       <c r="B29">
-        <v>0.42830593424911062</v>
+        <v>0.42830591702343612</v>
       </c>
       <c r="C29">
-        <v>0.48594555921399668</v>
+        <v>0.48594555869191192</v>
       </c>
       <c r="D29">
-        <v>0.49109875151938293</v>
+        <v>0.49109875028303801</v>
       </c>
       <c r="E29">
-        <v>0.51580068780360755</v>
+        <v>0.51580068747582641</v>
       </c>
       <c r="F29">
-        <v>0.51788896269479301</v>
+        <v>0.5178889607240168</v>
       </c>
       <c r="G29">
-        <v>0.51019934872703798</v>
+        <v>0.51019934720418114</v>
       </c>
       <c r="H29">
-        <v>0.50768941055962935</v>
+        <v>0.50768941362305908</v>
       </c>
       <c r="I29">
-        <v>0.50308242283971394</v>
+        <v>0.50308242258930802</v>
       </c>
       <c r="J29">
-        <v>0.51391605663294826</v>
+        <v>0.51391605492551817</v>
       </c>
       <c r="K29">
-        <v>0.50914488190950336</v>
+        <v>0.5091448789121229</v>
       </c>
       <c r="L29">
-        <v>0.49254501416219909</v>
+        <v>0.49254500861050549</v>
       </c>
       <c r="M29">
-        <v>0.42740971677830891</v>
+        <v>0.42740970129471262</v>
       </c>
       <c r="N29">
-        <v>0.41211150955870213</v>
+        <v>0.41211149004804498</v>
       </c>
       <c r="O29">
-        <v>0.40467316118618352</v>
+        <v>0.40467313636363811</v>
       </c>
       <c r="P29">
-        <v>0.40242034631081619</v>
+        <v>0.40242031529106759</v>
       </c>
       <c r="Q29">
-        <v>0.40499617321696502</v>
+        <v>0.40499612125089041</v>
       </c>
       <c r="R29">
-        <v>0.40270974325315562</v>
+        <v>0.40270969764904518</v>
       </c>
     </row>
     <row r="30" spans="1:18" x14ac:dyDescent="0.25">
@@ -2188,55 +2188,55 @@
         <v>46</v>
       </c>
       <c r="B30">
-        <v>0.42836598283845218</v>
+        <v>0.42836596726858722</v>
       </c>
       <c r="C30">
-        <v>0.48594555921399668</v>
+        <v>0.48594555869191192</v>
       </c>
       <c r="D30">
-        <v>0.49056835026501422</v>
+        <v>0.49056834881260408</v>
       </c>
       <c r="E30">
-        <v>0.51470086938864601</v>
+        <v>0.51470087047308333</v>
       </c>
       <c r="F30">
-        <v>0.51761869495375812</v>
+        <v>0.51761869376080105</v>
       </c>
       <c r="G30">
-        <v>0.5095751340266671</v>
+        <v>0.50957513242787911</v>
       </c>
       <c r="H30">
-        <v>0.50843246116609753</v>
+        <v>0.50843246323739255</v>
       </c>
       <c r="I30">
-        <v>0.50282164538063201</v>
+        <v>0.50282164463750589</v>
       </c>
       <c r="J30">
-        <v>0.51704836713102298</v>
+        <v>0.51704836684593791</v>
       </c>
       <c r="K30">
-        <v>0.51268397971054358</v>
+        <v>0.51268398072305643</v>
       </c>
       <c r="L30">
-        <v>0.49585815305899078</v>
+        <v>0.49585815085217699</v>
       </c>
       <c r="M30">
-        <v>0.43037387782571401</v>
+        <v>0.43037386437466169</v>
       </c>
       <c r="N30">
-        <v>0.41562949455532727</v>
+        <v>0.41562947753326968</v>
       </c>
       <c r="O30">
-        <v>0.40870432100148019</v>
+        <v>0.40870429919817902</v>
       </c>
       <c r="P30">
-        <v>0.40610755915014018</v>
+        <v>0.40610753566305707</v>
       </c>
       <c r="Q30">
-        <v>0.40607026527137008</v>
+        <v>0.40607023809085852</v>
       </c>
       <c r="R30">
-        <v>0.40188037506755819</v>
+        <v>0.40188034000265699</v>
       </c>
     </row>
     <row r="31" spans="1:18" x14ac:dyDescent="0.25">
@@ -2244,55 +2244,55 @@
         <v>47</v>
       </c>
       <c r="B31">
-        <v>0.43156295318636789</v>
+        <v>0.43156293853259431</v>
       </c>
       <c r="C31">
-        <v>0.48594555921399668</v>
+        <v>0.48594555869191192</v>
       </c>
       <c r="D31">
-        <v>0.49153778706848872</v>
+        <v>0.49153778604134418</v>
       </c>
       <c r="E31">
-        <v>0.51511182289253643</v>
+        <v>0.51511182237071529</v>
       </c>
       <c r="F31">
-        <v>0.51706185718216091</v>
+        <v>0.51706185522135195</v>
       </c>
       <c r="G31">
-        <v>0.50895500715006758</v>
+        <v>0.50895500478890598</v>
       </c>
       <c r="H31">
-        <v>0.50720373751275649</v>
+        <v>0.50720373951734909</v>
       </c>
       <c r="I31">
-        <v>0.5015370170926623</v>
+        <v>0.50153701570115816</v>
       </c>
       <c r="J31">
-        <v>0.51327177177469507</v>
+        <v>0.51327177025134885</v>
       </c>
       <c r="K31">
-        <v>0.50896645114546035</v>
+        <v>0.50896644628641663</v>
       </c>
       <c r="L31">
-        <v>0.49240108883206429</v>
+        <v>0.49240108384361941</v>
       </c>
       <c r="M31">
-        <v>0.43184864312999821</v>
+        <v>0.43184862943743813</v>
       </c>
       <c r="N31">
-        <v>0.41531307485617819</v>
+        <v>0.41531305787830869</v>
       </c>
       <c r="O31">
-        <v>0.40832568516423928</v>
+        <v>0.40832566701495587</v>
       </c>
       <c r="P31">
-        <v>0.40284074076993243</v>
+        <v>0.40284072052227871</v>
       </c>
       <c r="Q31">
-        <v>0.4047374832315439</v>
+        <v>0.4047374779618787</v>
       </c>
       <c r="R31">
-        <v>0.39901834935250208</v>
+        <v>0.39901832416401373</v>
       </c>
     </row>
     <row r="32" spans="1:18" x14ac:dyDescent="0.25">
@@ -2300,55 +2300,55 @@
         <v>48</v>
       </c>
       <c r="B32">
-        <v>0.44034820542876751</v>
+        <v>0.44034818632816891</v>
       </c>
       <c r="C32">
-        <v>0.48594555921399668</v>
+        <v>0.48594555869191192</v>
       </c>
       <c r="D32">
-        <v>0.49094532016184578</v>
+        <v>0.49094531879273978</v>
       </c>
       <c r="E32">
-        <v>0.51548311618794729</v>
+        <v>0.51548311532580215</v>
       </c>
       <c r="F32">
-        <v>0.51817797464646886</v>
+        <v>0.5181779725838469</v>
       </c>
       <c r="G32">
-        <v>0.51032694379816457</v>
+        <v>0.51032694204872675</v>
       </c>
       <c r="H32">
-        <v>0.50806061535316327</v>
+        <v>0.50806061549492787</v>
       </c>
       <c r="I32">
-        <v>0.50237617463211603</v>
+        <v>0.50237617360562326</v>
       </c>
       <c r="J32">
-        <v>0.51703597477103735</v>
+        <v>0.51703597322344408</v>
       </c>
       <c r="K32">
-        <v>0.50590073542233382</v>
+        <v>0.5059007312918451</v>
       </c>
       <c r="L32">
-        <v>0.48898233617644671</v>
+        <v>0.48898232929545232</v>
       </c>
       <c r="M32">
-        <v>0.43172607364412813</v>
+        <v>0.431726054635098</v>
       </c>
       <c r="N32">
-        <v>0.41594602117936469</v>
+        <v>0.41594599518745379</v>
       </c>
       <c r="O32">
-        <v>0.40978096617440662</v>
+        <v>0.40978093295553092</v>
       </c>
       <c r="P32">
-        <v>0.41177486850295719</v>
+        <v>0.41177483104277618</v>
       </c>
       <c r="Q32">
-        <v>0.42084939671058119</v>
+        <v>0.42084934920345041</v>
       </c>
       <c r="R32">
-        <v>0.42450027034088672</v>
+        <v>0.42450020718699538</v>
       </c>
     </row>
     <row r="33" spans="1:18" x14ac:dyDescent="0.25">
@@ -2356,55 +2356,55 @@
         <v>49</v>
       </c>
       <c r="B33">
-        <v>0.43564505322639019</v>
+        <v>0.43564503574727731</v>
       </c>
       <c r="C33">
-        <v>0.48594555921399668</v>
+        <v>0.48594555869191192</v>
       </c>
       <c r="D33">
-        <v>0.49124882340209602</v>
+        <v>0.49124882194619901</v>
       </c>
       <c r="E33">
-        <v>0.51663095758372679</v>
+        <v>0.51663095908351231</v>
       </c>
       <c r="F33">
-        <v>0.51958425520759977</v>
+        <v>0.51958425348762205</v>
       </c>
       <c r="G33">
-        <v>0.51123185443573149</v>
+        <v>0.51123185189124565</v>
       </c>
       <c r="H33">
-        <v>0.50839531697940454</v>
+        <v>0.50839532017246514</v>
       </c>
       <c r="I33">
-        <v>0.50358748021699418</v>
+        <v>0.50358748073648985</v>
       </c>
       <c r="J33">
-        <v>0.51702983258543855</v>
+        <v>0.51702983155541304</v>
       </c>
       <c r="K33">
-        <v>0.50812362308011239</v>
+        <v>0.50812362121397614</v>
       </c>
       <c r="L33">
-        <v>0.49157923489052519</v>
+        <v>0.4915792289306451</v>
       </c>
       <c r="M33">
-        <v>0.42845460371542771</v>
+        <v>0.42845458663294428</v>
       </c>
       <c r="N33">
-        <v>0.41483293690998307</v>
+        <v>0.41483291335118072</v>
       </c>
       <c r="O33">
-        <v>0.40862003984777667</v>
+        <v>0.40862001161663752</v>
       </c>
       <c r="P33">
-        <v>0.41118011766856122</v>
+        <v>0.41118008258922623</v>
       </c>
       <c r="Q33">
-        <v>0.41800496465750342</v>
+        <v>0.41800492076377632</v>
       </c>
       <c r="R33">
-        <v>0.42282489638831022</v>
+        <v>0.42282484467237907</v>
       </c>
     </row>
     <row r="34" spans="1:18" x14ac:dyDescent="0.25">
@@ -2412,55 +2412,55 @@
         <v>50</v>
       </c>
       <c r="B34">
-        <v>0.44445866963454728</v>
+        <v>0.44445865013920688</v>
       </c>
       <c r="C34">
-        <v>0.48594555921399668</v>
+        <v>0.48594555869191192</v>
       </c>
       <c r="D34">
-        <v>0.49122108915430251</v>
+        <v>0.49122108751707821</v>
       </c>
       <c r="E34">
-        <v>0.51564082080001061</v>
+        <v>0.51564082021511914</v>
       </c>
       <c r="F34">
-        <v>0.51854939250015686</v>
+        <v>0.51854939029629887</v>
       </c>
       <c r="G34">
-        <v>0.51074233321774987</v>
+        <v>0.51074233121841528</v>
       </c>
       <c r="H34">
-        <v>0.50842564910401666</v>
+        <v>0.50842564305949767</v>
       </c>
       <c r="I34">
-        <v>0.50238105602166994</v>
+        <v>0.50238105609715444</v>
       </c>
       <c r="J34">
-        <v>0.51461215460054111</v>
+        <v>0.51461215469551613</v>
       </c>
       <c r="K34">
-        <v>0.50794795933492576</v>
+        <v>0.50794795189723407</v>
       </c>
       <c r="L34">
-        <v>0.49355031009859551</v>
+        <v>0.49355030370810282</v>
       </c>
       <c r="M34">
-        <v>0.43353772374017779</v>
+        <v>0.43353770554997278</v>
       </c>
       <c r="N34">
-        <v>0.41757527057124483</v>
+        <v>0.41757524727433259</v>
       </c>
       <c r="O34">
-        <v>0.40905687555455927</v>
+        <v>0.40905684732712511</v>
       </c>
       <c r="P34">
-        <v>0.40947671446480921</v>
+        <v>0.40947668150206801</v>
       </c>
       <c r="Q34">
-        <v>0.41506095769804008</v>
+        <v>0.41506091617856983</v>
       </c>
       <c r="R34">
-        <v>0.41669677844207609</v>
+        <v>0.41669672930211299</v>
       </c>
     </row>
     <row r="35" spans="1:18" x14ac:dyDescent="0.25">
@@ -2468,55 +2468,55 @@
         <v>51</v>
       </c>
       <c r="B35">
-        <v>0.44212103897975419</v>
+        <v>0.44212102451297752</v>
       </c>
       <c r="C35">
-        <v>0.48594555921399668</v>
+        <v>0.48594555869191192</v>
       </c>
       <c r="D35">
-        <v>0.49071966734472511</v>
+        <v>0.49071966602224393</v>
       </c>
       <c r="E35">
-        <v>0.51541478831808318</v>
+        <v>0.51541478791464501</v>
       </c>
       <c r="F35">
-        <v>0.51811759739626917</v>
+        <v>0.51811759528611889</v>
       </c>
       <c r="G35">
-        <v>0.51035410029965267</v>
+        <v>0.51035409832299905</v>
       </c>
       <c r="H35">
-        <v>0.50903622376296542</v>
+        <v>0.50903622675348137</v>
       </c>
       <c r="I35">
-        <v>0.50344278242374108</v>
+        <v>0.50344278747470106</v>
       </c>
       <c r="J35">
-        <v>0.51451853342959897</v>
+        <v>0.51451852951047838</v>
       </c>
       <c r="K35">
-        <v>0.50727257660921954</v>
+        <v>0.50727257373239154</v>
       </c>
       <c r="L35">
-        <v>0.49183082701209452</v>
+        <v>0.49183082224867869</v>
       </c>
       <c r="M35">
-        <v>0.42869847422318841</v>
+        <v>0.42869845992594402</v>
       </c>
       <c r="N35">
-        <v>0.41331945193115222</v>
+        <v>0.41331943295964108</v>
       </c>
       <c r="O35">
-        <v>0.40559842017559089</v>
+        <v>0.40559839556329957</v>
       </c>
       <c r="P35">
-        <v>0.4056074006080489</v>
+        <v>0.40560737500972632</v>
       </c>
       <c r="Q35">
-        <v>0.40979386839227427</v>
+        <v>0.40979383545194781</v>
       </c>
       <c r="R35">
-        <v>0.41173949573377172</v>
+        <v>0.41173945257310229</v>
       </c>
     </row>
     <row r="36" spans="1:18" x14ac:dyDescent="0.25">
@@ -2524,55 +2524,55 @@
         <v>52</v>
       </c>
       <c r="B36">
-        <v>0.4349566203011388</v>
+        <v>0.43495660487307058</v>
       </c>
       <c r="C36">
-        <v>0.48594555921399668</v>
+        <v>0.48594555869191192</v>
       </c>
       <c r="D36">
-        <v>0.49117238703708038</v>
+        <v>0.49117238475080849</v>
       </c>
       <c r="E36">
-        <v>0.51629998747460826</v>
+        <v>0.51629998625590312</v>
       </c>
       <c r="F36">
-        <v>0.51946627692433278</v>
+        <v>0.51946627511539689</v>
       </c>
       <c r="G36">
-        <v>0.51105221562021852</v>
+        <v>0.51105221506247245</v>
       </c>
       <c r="H36">
-        <v>0.50854461191671518</v>
+        <v>0.50854461306005017</v>
       </c>
       <c r="I36">
-        <v>0.50238405844104439</v>
+        <v>0.50238405517299134</v>
       </c>
       <c r="J36">
-        <v>0.51439617683401184</v>
+        <v>0.51439618482875038</v>
       </c>
       <c r="K36">
-        <v>0.50846279054444965</v>
+        <v>0.5084627865734721</v>
       </c>
       <c r="L36">
-        <v>0.49385402514583338</v>
+        <v>0.4938540213528369</v>
       </c>
       <c r="M36">
-        <v>0.43412631323835688</v>
+        <v>0.43412629894010168</v>
       </c>
       <c r="N36">
-        <v>0.41930163338938292</v>
+        <v>0.41930161744631173</v>
       </c>
       <c r="O36">
-        <v>0.40927828716210718</v>
+        <v>0.40927826888987112</v>
       </c>
       <c r="P36">
-        <v>0.40437924209511539</v>
+        <v>0.40437921877992572</v>
       </c>
       <c r="Q36">
-        <v>0.4052297780432349</v>
+        <v>0.40522975290107038</v>
       </c>
       <c r="R36">
-        <v>0.40022957155273781</v>
+        <v>0.40022954178389752</v>
       </c>
     </row>
     <row r="37" spans="1:18" x14ac:dyDescent="0.25">
@@ -2580,55 +2580,55 @@
         <v>53</v>
       </c>
       <c r="B37">
-        <v>0.49782313095488639</v>
+        <v>0.49782312649356131</v>
       </c>
       <c r="C37">
-        <v>0.48594555921399668</v>
+        <v>0.48594555869191192</v>
       </c>
       <c r="D37">
-        <v>0.4919198086754264</v>
+        <v>0.49191980661618512</v>
       </c>
       <c r="E37">
-        <v>0.52190961635902278</v>
+        <v>0.52190961822159987</v>
       </c>
       <c r="F37">
-        <v>0.50898344348839064</v>
+        <v>0.50898343168295657</v>
       </c>
       <c r="G37">
-        <v>0.49776038660198918</v>
+        <v>0.49776037580138788</v>
       </c>
       <c r="H37">
-        <v>0.50084029270245767</v>
+        <v>0.50084027503170758</v>
       </c>
       <c r="I37">
-        <v>0.49828410593836642</v>
+        <v>0.49828407024335358</v>
       </c>
       <c r="J37">
-        <v>0.47544934867927952</v>
+        <v>0.47544928282744731</v>
       </c>
       <c r="K37">
-        <v>0.47212695572113922</v>
+        <v>0.47212688756429327</v>
       </c>
       <c r="L37">
-        <v>0.47113862955828317</v>
+        <v>0.47113856440527191</v>
       </c>
       <c r="M37">
-        <v>0.46510684027846633</v>
+        <v>0.46510679392100951</v>
       </c>
       <c r="N37">
-        <v>0.46793742549203171</v>
+        <v>0.46793735421122878</v>
       </c>
       <c r="O37">
-        <v>0.47701509017744198</v>
+        <v>0.47701425515929202</v>
       </c>
       <c r="P37">
-        <v>0.46750780612300252</v>
+        <v>0.46750773923012751</v>
       </c>
       <c r="Q37">
-        <v>0.46148691751296589</v>
+        <v>0.4614868102514279</v>
       </c>
       <c r="R37">
-        <v>0.45793509749039019</v>
+        <v>0.4579349467324057</v>
       </c>
     </row>
     <row r="38" spans="1:18" x14ac:dyDescent="0.25">
@@ -2636,55 +2636,55 @@
         <v>54</v>
       </c>
       <c r="B38">
-        <v>0.44703539543075949</v>
+        <v>0.44703537880018918</v>
       </c>
       <c r="C38">
-        <v>0.48594555921399668</v>
+        <v>0.48594555869191192</v>
       </c>
       <c r="D38">
-        <v>0.49140660858498891</v>
+        <v>0.49140660661784602</v>
       </c>
       <c r="E38">
-        <v>0.51724961450647533</v>
+        <v>0.51724961510506673</v>
       </c>
       <c r="F38">
-        <v>0.51122350542524009</v>
+        <v>0.51122350205332667</v>
       </c>
       <c r="G38">
-        <v>0.49096581673241729</v>
+        <v>0.49096581828122171</v>
       </c>
       <c r="H38">
-        <v>0.47443577002934012</v>
+        <v>0.47443576454517788</v>
       </c>
       <c r="I38">
-        <v>0.45091442582629798</v>
+        <v>0.45091441293130968</v>
       </c>
       <c r="J38">
-        <v>0.4136228713402178</v>
+        <v>0.41362284912295522</v>
       </c>
       <c r="K38">
-        <v>0.41761538732219028</v>
+        <v>0.41761534961611008</v>
       </c>
       <c r="L38">
-        <v>0.42927386151298141</v>
+        <v>0.4292738145702818</v>
       </c>
       <c r="M38">
-        <v>0.43469465607819568</v>
+        <v>0.43469460297724738</v>
       </c>
       <c r="N38">
-        <v>0.43114313465675208</v>
+        <v>0.43114307521654888</v>
       </c>
       <c r="O38">
-        <v>0.42994224017711091</v>
+        <v>0.4299421860654884</v>
       </c>
       <c r="P38">
-        <v>0.42019082020596749</v>
+        <v>0.42019078541071042</v>
       </c>
       <c r="Q38">
-        <v>0.41321159801345908</v>
+        <v>0.41321155075687921</v>
       </c>
       <c r="R38">
-        <v>0.41173407890628588</v>
+        <v>0.41173402958521382</v>
       </c>
     </row>
     <row r="39" spans="1:18" x14ac:dyDescent="0.25">
@@ -2692,55 +2692,55 @@
         <v>55</v>
       </c>
       <c r="B39">
-        <v>0.44541558320593488</v>
+        <v>0.44541557894798078</v>
       </c>
       <c r="C39">
-        <v>0.48594555921399668</v>
+        <v>0.48594555869191192</v>
       </c>
       <c r="D39">
-        <v>0.49178728290194468</v>
+        <v>0.49178728225797502</v>
       </c>
       <c r="E39">
-        <v>0.51664599939489464</v>
+        <v>0.51664600065427269</v>
       </c>
       <c r="F39">
-        <v>0.50950185562830241</v>
+        <v>0.50950185527471048</v>
       </c>
       <c r="G39">
-        <v>0.48756013242173701</v>
+        <v>0.48756015319028978</v>
       </c>
       <c r="H39">
-        <v>0.47830999788559858</v>
+        <v>0.47831005326972659</v>
       </c>
       <c r="I39">
-        <v>0.45683451518874008</v>
+        <v>0.45683451141045389</v>
       </c>
       <c r="J39">
-        <v>0.42258843917474131</v>
+        <v>0.42258842788524631</v>
       </c>
       <c r="K39">
-        <v>0.42122583718849732</v>
+        <v>0.4212258637268485</v>
       </c>
       <c r="L39">
-        <v>0.41724190607971978</v>
+        <v>0.41724190697384977</v>
       </c>
       <c r="M39">
-        <v>0.41643795231477992</v>
+        <v>0.41643791618596171</v>
       </c>
       <c r="N39">
-        <v>0.41540675938758798</v>
+        <v>0.41540672968778869</v>
       </c>
       <c r="O39">
-        <v>0.40598968838143951</v>
+        <v>0.40598964997751902</v>
       </c>
       <c r="P39">
-        <v>0.40456736366579787</v>
+        <v>0.4045673123228643</v>
       </c>
       <c r="Q39">
-        <v>0.40673163586730332</v>
+        <v>0.4067315828910496</v>
       </c>
       <c r="R39">
-        <v>0.40433324580421642</v>
+        <v>0.40433318251718292</v>
       </c>
     </row>
     <row r="40" spans="1:18" x14ac:dyDescent="0.25">
@@ -2748,55 +2748,55 @@
         <v>56</v>
       </c>
       <c r="B40">
-        <v>0.48743337502873452</v>
+        <v>0.48743335987097391</v>
       </c>
       <c r="C40">
-        <v>0.48594555921399668</v>
+        <v>0.48594555869191192</v>
       </c>
       <c r="D40">
-        <v>0.49632535162293528</v>
+        <v>0.49632534880785389</v>
       </c>
       <c r="E40">
-        <v>0.50040299419778711</v>
+        <v>0.5004029937255382</v>
       </c>
       <c r="F40">
-        <v>0.47916986986196419</v>
+        <v>0.47916986836035069</v>
       </c>
       <c r="G40">
-        <v>0.48831537854992157</v>
+        <v>0.48831538432107741</v>
       </c>
       <c r="H40">
-        <v>0.46082537880174362</v>
+        <v>0.46082536487436859</v>
       </c>
       <c r="I40">
-        <v>0.44389162383421532</v>
+        <v>0.44389160309694969</v>
       </c>
       <c r="J40">
-        <v>0.45251527608069569</v>
+        <v>0.45251523223355311</v>
       </c>
       <c r="K40">
-        <v>0.46497635724029601</v>
+        <v>0.46497629819483283</v>
       </c>
       <c r="L40">
-        <v>0.46004473290108883</v>
+        <v>0.46004469715326562</v>
       </c>
       <c r="M40">
-        <v>0.4467327645774139</v>
+        <v>0.44673270474666688</v>
       </c>
       <c r="N40">
-        <v>0.44418617054271647</v>
+        <v>0.44418613545459951</v>
       </c>
       <c r="O40">
-        <v>0.43608835388039752</v>
+        <v>0.43608831378874519</v>
       </c>
       <c r="P40">
-        <v>0.43717019265143742</v>
+        <v>0.43717012269130501</v>
       </c>
       <c r="Q40">
-        <v>0.44579380711079591</v>
+        <v>0.44579370980079108</v>
       </c>
       <c r="R40">
-        <v>0.46089319832122821</v>
+        <v>0.46089306842908512</v>
       </c>
     </row>
     <row r="41" spans="1:18" x14ac:dyDescent="0.25">
@@ -2804,55 +2804,55 @@
         <v>57</v>
       </c>
       <c r="B41">
-        <v>0.49527175250890521</v>
+        <v>0.49527175092661618</v>
       </c>
       <c r="C41">
-        <v>0.48594555921399668</v>
+        <v>0.48594555869191192</v>
       </c>
       <c r="D41">
-        <v>0.49511011312985459</v>
+        <v>0.49511011139463751</v>
       </c>
       <c r="E41">
-        <v>0.53416831469080583</v>
+        <v>0.53416831377720109</v>
       </c>
       <c r="F41">
-        <v>0.51722437984661973</v>
+        <v>0.51722437799343457</v>
       </c>
       <c r="G41">
-        <v>0.52785258040998762</v>
+        <v>0.52785257608605274</v>
       </c>
       <c r="H41">
-        <v>0.51179357880375043</v>
+        <v>0.51179357949427684</v>
       </c>
       <c r="I41">
-        <v>0.51066567259242179</v>
+        <v>0.51066567580079814</v>
       </c>
       <c r="J41">
-        <v>0.50238423777643104</v>
+        <v>0.50238423938831889</v>
       </c>
       <c r="K41">
-        <v>0.48401437857485963</v>
+        <v>0.48401437936164571</v>
       </c>
       <c r="L41">
-        <v>0.49353824638645799</v>
+        <v>0.49353824981526778</v>
       </c>
       <c r="M41">
-        <v>0.50009862705042774</v>
+        <v>0.50009862475868538</v>
       </c>
       <c r="N41">
-        <v>0.49808495445296741</v>
+        <v>0.49808494474329917</v>
       </c>
       <c r="O41">
-        <v>0.50500033943203682</v>
+        <v>0.50500032080682489</v>
       </c>
       <c r="P41">
-        <v>0.517845955471122</v>
+        <v>0.51784593987113292</v>
       </c>
       <c r="Q41">
-        <v>0.51702940575244716</v>
+        <v>0.51702938490682004</v>
       </c>
       <c r="R41">
-        <v>0.51893654189461158</v>
+        <v>0.51893652056049666</v>
       </c>
     </row>
     <row r="42" spans="1:18" x14ac:dyDescent="0.25">
@@ -2860,55 +2860,55 @@
         <v>58</v>
       </c>
       <c r="B42">
-        <v>0.42253597756503952</v>
+        <v>0.42253598282731158</v>
       </c>
       <c r="C42">
-        <v>0.48594555921399668</v>
+        <v>0.48594555869191192</v>
       </c>
       <c r="D42">
-        <v>0.48600140502236799</v>
+        <v>0.48600140450788148</v>
       </c>
       <c r="E42">
-        <v>0.50661525757321746</v>
+        <v>0.50661525524343731</v>
       </c>
       <c r="F42">
-        <v>0.53039151563451981</v>
+        <v>0.53039152307916682</v>
       </c>
       <c r="G42">
-        <v>0.47758224751983391</v>
+        <v>0.47758224458368009</v>
       </c>
       <c r="H42">
-        <v>0.44872758350825948</v>
+        <v>0.44872758891639519</v>
       </c>
       <c r="I42">
-        <v>0.43577907553744633</v>
+        <v>0.43577908717590053</v>
       </c>
       <c r="J42">
-        <v>0.40125502026986731</v>
+        <v>0.40125502614120501</v>
       </c>
       <c r="K42">
-        <v>0.39894263342203851</v>
+        <v>0.39894264244690458</v>
       </c>
       <c r="L42">
-        <v>0.40424457117904711</v>
+        <v>0.40424458082702069</v>
       </c>
       <c r="M42">
-        <v>0.38866201897263131</v>
+        <v>0.38866202625037871</v>
       </c>
       <c r="N42">
-        <v>0.38617695684920889</v>
+        <v>0.38617696163974918</v>
       </c>
       <c r="O42">
-        <v>0.38965707784482789</v>
+        <v>0.38965707684008161</v>
       </c>
       <c r="P42">
-        <v>0.39216898820542812</v>
+        <v>0.39216898519267579</v>
       </c>
       <c r="Q42">
-        <v>0.39181191558158168</v>
+        <v>0.39181190608309041</v>
       </c>
       <c r="R42">
-        <v>0.39575228446973609</v>
+        <v>0.39575229059537159</v>
       </c>
     </row>
     <row r="43" spans="1:18" x14ac:dyDescent="0.25">
@@ -2916,55 +2916,55 @@
         <v>59</v>
       </c>
       <c r="B43">
-        <v>0.44851976172644958</v>
+        <v>0.44851976491433382</v>
       </c>
       <c r="C43">
-        <v>0.48594555921399668</v>
+        <v>0.48594555869191192</v>
       </c>
       <c r="D43">
-        <v>0.48815377260013287</v>
+        <v>0.48815377147493189</v>
       </c>
       <c r="E43">
-        <v>0.50599327566250929</v>
+        <v>0.50599327589396337</v>
       </c>
       <c r="F43">
-        <v>0.50092087399772034</v>
+        <v>0.50092086973424732</v>
       </c>
       <c r="G43">
-        <v>0.47241513008970509</v>
+        <v>0.47241512954591169</v>
       </c>
       <c r="H43">
-        <v>0.43475859359608682</v>
+        <v>0.43475859955998147</v>
       </c>
       <c r="I43">
-        <v>0.42681391290918608</v>
+        <v>0.4268139162276729</v>
       </c>
       <c r="J43">
-        <v>0.41167163720432332</v>
+        <v>0.41167164133925072</v>
       </c>
       <c r="K43">
-        <v>0.4096004610723129</v>
+        <v>0.4096004621123624</v>
       </c>
       <c r="L43">
-        <v>0.41924294059576672</v>
+        <v>0.41924294585682959</v>
       </c>
       <c r="M43">
-        <v>0.41100971559088462</v>
+        <v>0.4110097118712539</v>
       </c>
       <c r="N43">
-        <v>0.40825337835860198</v>
+        <v>0.40825337019753533</v>
       </c>
       <c r="O43">
-        <v>0.41033959415354382</v>
+        <v>0.41033957996539389</v>
       </c>
       <c r="P43">
-        <v>0.4167864181533153</v>
+        <v>0.41678639796102879</v>
       </c>
       <c r="Q43">
-        <v>0.42448042841323108</v>
+        <v>0.42448040187337072</v>
       </c>
       <c r="R43">
-        <v>0.4295930515079418</v>
+        <v>0.42959301627334312</v>
       </c>
     </row>
   </sheetData>
